--- a/data/cci/cci-org.xlsx
+++ b/data/cci/cci-org.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{62A10CED-EE1C-6944-94A2-AC4C7CB24793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E9E55C7-FC5F-4E00-9E35-D3AA7DA9187C}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{62A10CED-EE1C-6944-94A2-AC4C7CB24793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F44C3439-359A-48C0-8E25-F5595B8E7517}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{04F743D1-7C0F-1C43-BF25-7C0E63F3FDA6}"/>
+    <workbookView xWindow="3570" yWindow="2700" windowWidth="34515" windowHeight="15285" xr2:uid="{04F743D1-7C0F-1C43-BF25-7C0E63F3FDA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="330">
   <si>
     <t>URI</t>
   </si>
@@ -1020,6 +1020,15 @@
   </si>
   <si>
     <t>University of Porto</t>
+  </si>
+  <si>
+    <t>org110</t>
+  </si>
+  <si>
+    <t>IPMA</t>
+  </si>
+  <si>
+    <t>Instituto Português do Mar e da Atmosfera</t>
   </si>
 </sst>
 </file>
@@ -1427,7 +1436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F04911A-215F-424B-BD95-9DCC009C6955}">
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5546875" customWidth="1"/>
@@ -2914,6 +2923,20 @@
         <v>121739996</v>
       </c>
     </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>327</v>
+      </c>
+      <c r="B110" t="s">
+        <v>329</v>
+      </c>
+      <c r="C110" t="s">
+        <v>328</v>
+      </c>
+      <c r="E110">
+        <v>403820653</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0.39409448818897636" bottom="0.39409448818897636" header="0" footer="0"/>
   <headerFooter>

--- a/data/cci/cci-org.xlsx
+++ b/data/cci/cci-org.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{62A10CED-EE1C-6944-94A2-AC4C7CB24793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F44C3439-359A-48C0-8E25-F5595B8E7517}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{62A10CED-EE1C-6944-94A2-AC4C7CB24793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37DAECF3-DC84-47AB-BD80-3DE0C354F824}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="2700" windowWidth="34515" windowHeight="15285" xr2:uid="{04F743D1-7C0F-1C43-BF25-7C0E63F3FDA6}"/>
+    <workbookView xWindow="38280" yWindow="-60" windowWidth="38640" windowHeight="21120" xr2:uid="{04F743D1-7C0F-1C43-BF25-7C0E63F3FDA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="335">
   <si>
     <t>URI</t>
   </si>
@@ -1029,6 +1029,21 @@
   </si>
   <si>
     <t>Instituto Português do Mar e da Atmosfera</t>
+  </si>
+  <si>
+    <t>org111</t>
+  </si>
+  <si>
+    <t>IFREMER-LOPS</t>
+  </si>
+  <si>
+    <t>Institut Français pour la Recherche et l Exploitation de la MER, Laboratoire d'Océanographie Physique et Spatiale</t>
+  </si>
+  <si>
+    <t>org112</t>
+  </si>
+  <si>
+    <t>University of Hawaii</t>
   </si>
 </sst>
 </file>
@@ -1096,8 +1111,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading" xfId="1" xr:uid="{2D607FC0-E9E2-9140-ADEA-4D49D59B5327}"/>
@@ -1436,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F04911A-215F-424B-BD95-9DCC009C6955}">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5546875" customWidth="1"/>
@@ -2937,8 +2953,29 @@
         <v>403820653</v>
       </c>
     </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>330</v>
+      </c>
+      <c r="B111" t="s">
+        <v>332</v>
+      </c>
+      <c r="C111" t="s">
+        <v>331</v>
+      </c>
+      <c r="E111" s="1"/>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>333</v>
+      </c>
+      <c r="B112" t="s">
+        <v>334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0.39409448818897636" bottom="0.39409448818897636" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
